--- a/input.xlsx
+++ b/input.xlsx
@@ -398,19 +398,19 @@
         <v>6</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/input.xlsx
+++ b/input.xlsx
@@ -20,24 +20,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t xml:space="preserve">TEAMS</t>
   </si>
   <si>
-    <t xml:space="preserve">Category 1</t>
+    <t xml:space="preserve">Pelouse</t>
   </si>
   <si>
-    <t xml:space="preserve">Category 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category 3</t>
+    <t xml:space="preserve">Pitch</t>
   </si>
   <si>
     <t xml:space="preserve">Category 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catégorie 1</t>
   </si>
   <si>
     <t xml:space="preserve">DJ SNAKE - 10 mai 2025</t>
@@ -386,32 +380,23 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="B2" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
-      <c r="E2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="E2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8"/>
